--- a/Input Hopfner.xlsx
+++ b/Input Hopfner.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\martinahopfner.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC93BDA-CB60-4499-BCBF-E7C221C2D560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{EEC93BDA-CB60-4499-BCBF-E7C221C2D560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{288CBCB6-C84A-4DAD-886F-FB9B561DE3A4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" xr2:uid="{5BA2C9A2-01C8-41FE-A486-6418B9B1B1A5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="77">
   <si>
     <t>img</t>
   </si>
@@ -217,6 +217,13 @@
     <t>Scan: Cathrin Sonntag</t>
   </si>
   <si>
+    <t>Nymph_01.jpg</t>
+  </si>
+  <si>
+    <t>Nymph
+Editorial for Blumenhaus Magazine</t>
+  </si>
+  <si>
     <t>Photo: Marry Rozzi
 Styling: Sara Medali
 Hair: Yui Ozaki
@@ -225,36 +232,102 @@
 Model: Lena Ballayre | New Wave Management</t>
   </si>
   <si>
+    <t>Nymph_02.jpg</t>
+  </si>
+  <si>
     <t>Photo: Marry Rozzi
 Styling: Sara Medali
 Set: Raphaëlle Daguerre</t>
   </si>
   <si>
+    <t>Nymph_03.jpg</t>
+  </si>
+  <si>
+    <t>Nymph_04.jpg</t>
+  </si>
+  <si>
     <t>Photo: Marry Rozzi
 Set: Raphaëlle Daguerre</t>
   </si>
   <si>
-    <t>Nymph_01.jpg</t>
-  </si>
-  <si>
-    <t>Nymph_02.jpg</t>
-  </si>
-  <si>
-    <t>Nymph_03.jpg</t>
-  </si>
-  <si>
-    <t>Nymph_04.jpg</t>
-  </si>
-  <si>
-    <t>Nymph
-Editorial for Blumenhaus Magazine</t>
+    <t>Matter-of-nuance_01.jpg</t>
+  </si>
+  <si>
+    <t>Matter of Nuance
+Editorial for ONE Magazine</t>
+  </si>
+  <si>
+    <t>Photo: Kornelia Konieczka
+H+M: Bianca Hartkopf
+Set + Textures: Cathrin Sonntag
+Light: Gabriela Bluske
+Model: Magatte Diop | Modelwerk</t>
+  </si>
+  <si>
+    <t>Matter-of-nuance_02.jpg</t>
+  </si>
+  <si>
+    <t>Matter-of-nuance_03.jpg</t>
+  </si>
+  <si>
+    <t>Photo: Kornelia Konieczka
+H+M: Bianca Hartkopf
+Set: Cathrin Sonntag
+Light: Gabriela Bluske
+Model: Magatte Diop | Modelwerk</t>
+  </si>
+  <si>
+    <t>Matter-of-nuance_04.jpg</t>
+  </si>
+  <si>
+    <t>Matter-of-nuance_05.jpg</t>
+  </si>
+  <si>
+    <t>Photo: Kornelia Konieczka
+H+M: Bianca Hartkopf
+Set: Cathrin Sonntag
+Light: Gabriela Bluske
+Model: Magatte Diop | Modelwerk
+Glass Earring: Claraswears</t>
+  </si>
+  <si>
+    <t>Matter-of-nuance_06.jpg</t>
+  </si>
+  <si>
+    <t>Matter-of-nuance_07.jpg</t>
+  </si>
+  <si>
+    <t>Matter-of-nuance_08.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photo: Kornelia Konieczka
+Set : Cathrin Sonntag
+Light: Gabriela Bluske
+Glass Flower: Claraswears </t>
+  </si>
+  <si>
+    <t>Matter-of-nuance_09.jpg</t>
+  </si>
+  <si>
+    <t>Photo: Kornelia Konieczka
+Set : Cathrin Sonntag
+Light: Gabriela Bluske</t>
+  </si>
+  <si>
+    <t>Matter-of-nuance_10.jpg</t>
+  </si>
+  <si>
+    <t>Matter-of-nuance_11.jpg</t>
+  </si>
+  <si>
+    <t>Matter-of-nuance_12.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -320,15 +393,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -660,16 +730,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785963ED-F8C1-409E-94A9-D6B12E43F30E}">
-  <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I53"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="3" width="30.54296875" customWidth="1"/>
+    <col min="1" max="3" width="30.5703125" customWidth="1"/>
     <col min="4" max="4" width="39" style="7" customWidth="1"/>
-    <col min="6" max="6" width="33.26953125" customWidth="1"/>
-    <col min="8" max="8" width="30.54296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="7"/>
+    <col min="6" max="6" width="33.28515625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="7"/>
+    <col min="8" max="8" width="30.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -682,20 +754,20 @@
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="99.75" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -708,20 +780,20 @@
       <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
+      <c r="E2" s="6">
+        <v>0</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0</v>
+      </c>
+      <c r="G2" s="6">
         <v>1</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="99.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -734,20 +806,20 @@
       <c r="D3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
+      <c r="E3" s="6">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6">
         <v>1</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="99.75" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -760,17 +832,17 @@
       <c r="D4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E4" s="6">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="99.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -783,17 +855,17 @@
       <c r="D5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E5" s="6">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="99.75" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -806,17 +878,17 @@
       <c r="D6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E6" s="6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="99.75" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -829,17 +901,17 @@
       <c r="D7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="99.75" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
@@ -852,17 +924,17 @@
       <c r="D8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="99.75" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -875,26 +947,26 @@
       <c r="D9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="E9" s="6">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="6"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" ht="69.75" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -907,17 +979,17 @@
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="69.75" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
@@ -930,20 +1002,20 @@
       <c r="D12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2">
+      <c r="E12" s="6">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6">
         <v>0</v>
       </c>
       <c r="I12" s="4">
         <v>-5</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="69.75" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
@@ -956,17 +1028,17 @@
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E13" s="6">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="69.75" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
@@ -979,27 +1051,27 @@
       <c r="D14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="E14" s="6">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="6"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
       <c r="I15" s="2"/>
     </row>
-    <row r="16" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="99.75" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
@@ -1012,18 +1084,18 @@
       <c r="D16" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2">
+      <c r="E16" s="6">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6">
+        <v>0</v>
+      </c>
+      <c r="G16" s="6">
         <v>1</v>
       </c>
       <c r="I16" s="2"/>
     </row>
-    <row r="17" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="99.75" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>30</v>
       </c>
@@ -1036,18 +1108,18 @@
       <c r="D17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0</v>
-      </c>
-      <c r="G17" s="2">
+      <c r="E17" s="6">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6">
         <v>1</v>
       </c>
       <c r="I17" s="2"/>
     </row>
-    <row r="18" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="45" customHeight="1">
       <c r="A18" s="2" t="s">
         <v>31</v>
       </c>
@@ -1060,18 +1132,18 @@
       <c r="D18" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="2">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0</v>
-      </c>
-      <c r="G18" s="2">
+      <c r="E18" s="6">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6">
+        <v>0</v>
+      </c>
+      <c r="G18" s="6">
         <v>1</v>
       </c>
       <c r="I18" s="2"/>
     </row>
-    <row r="19" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="99.75" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>33</v>
       </c>
@@ -1084,18 +1156,18 @@
       <c r="D19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="2">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0</v>
-      </c>
-      <c r="G19" s="2">
+      <c r="E19" s="6">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0</v>
+      </c>
+      <c r="G19" s="6">
         <v>1</v>
       </c>
       <c r="I19" s="2"/>
     </row>
-    <row r="20" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="99.75" customHeight="1">
       <c r="A20" s="2" t="s">
         <v>34</v>
       </c>
@@ -1108,18 +1180,18 @@
       <c r="D20" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="2">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0</v>
-      </c>
-      <c r="G20" s="2">
+      <c r="E20" s="6">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6">
         <v>1</v>
       </c>
       <c r="I20" s="2"/>
     </row>
-    <row r="21" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="99.75" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>35</v>
       </c>
@@ -1132,18 +1204,18 @@
       <c r="D21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="2">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0</v>
-      </c>
-      <c r="G21" s="2">
+      <c r="E21" s="6">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6">
         <v>1</v>
       </c>
       <c r="I21" s="2"/>
     </row>
-    <row r="22" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="99.75" customHeight="1">
       <c r="A22" s="2" t="s">
         <v>36</v>
       </c>
@@ -1156,18 +1228,18 @@
       <c r="D22" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="2">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2">
+      <c r="E22" s="6">
+        <v>0</v>
+      </c>
+      <c r="F22" s="6">
+        <v>0</v>
+      </c>
+      <c r="G22" s="6">
         <v>1</v>
       </c>
       <c r="I22" s="2"/>
     </row>
-    <row r="23" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="99.75" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>37</v>
       </c>
@@ -1180,18 +1252,18 @@
       <c r="D23" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="2">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0</v>
-      </c>
-      <c r="G23" s="2">
+      <c r="E23" s="6">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6">
         <v>0</v>
       </c>
       <c r="I23" s="2"/>
     </row>
-    <row r="24" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="99.75" customHeight="1">
       <c r="A24" s="2" t="s">
         <v>38</v>
       </c>
@@ -1204,18 +1276,18 @@
       <c r="D24" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="2">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2">
-        <v>0</v>
-      </c>
-      <c r="G24" s="2">
+      <c r="E24" s="6">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6">
+        <v>0</v>
+      </c>
+      <c r="G24" s="6">
         <v>1</v>
       </c>
       <c r="I24" s="2"/>
     </row>
-    <row r="25" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="99.75" customHeight="1">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -1228,18 +1300,18 @@
       <c r="D25" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="2">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2">
+      <c r="E25" s="6">
+        <v>0</v>
+      </c>
+      <c r="F25" s="6">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6">
         <v>1</v>
       </c>
       <c r="I25" s="2"/>
     </row>
-    <row r="26" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="99.75" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>40</v>
       </c>
@@ -1252,18 +1324,18 @@
       <c r="D26" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="2">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2">
+      <c r="E26" s="6">
+        <v>0</v>
+      </c>
+      <c r="F26" s="6">
+        <v>0</v>
+      </c>
+      <c r="G26" s="6">
         <v>1</v>
       </c>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="99.75" customHeight="1">
       <c r="A27" s="2" t="s">
         <v>41</v>
       </c>
@@ -1276,28 +1348,28 @@
       <c r="D27" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E27" s="2">
-        <v>0</v>
-      </c>
-      <c r="F27" s="2">
-        <v>0</v>
-      </c>
-      <c r="G27" s="2">
+      <c r="E27" s="6">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6">
         <v>1</v>
       </c>
       <c r="I27" s="2"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="15">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="6"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
       <c r="I28" s="2"/>
     </row>
-    <row r="29" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="75" customHeight="1">
       <c r="A29" s="2" t="s">
         <v>42</v>
       </c>
@@ -1310,17 +1382,17 @@
       <c r="D29" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="2">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E29" s="6">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0</v>
+      </c>
+      <c r="G29" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="75" customHeight="1">
       <c r="A30" s="2" t="s">
         <v>45</v>
       </c>
@@ -1333,17 +1405,17 @@
       <c r="D30" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E30" s="2">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0</v>
-      </c>
-      <c r="G30" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E30" s="6">
+        <v>0</v>
+      </c>
+      <c r="F30" s="6">
+        <v>0</v>
+      </c>
+      <c r="G30" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="75" customHeight="1">
       <c r="A31" s="2" t="s">
         <v>46</v>
       </c>
@@ -1356,17 +1428,17 @@
       <c r="D31" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E31" s="2">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E31" s="6">
+        <v>0</v>
+      </c>
+      <c r="F31" s="6">
+        <v>0</v>
+      </c>
+      <c r="G31" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="75" customHeight="1">
       <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
@@ -1379,26 +1451,26 @@
       <c r="D32" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E32" s="2">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E32" s="6">
+        <v>0</v>
+      </c>
+      <c r="F32" s="6">
+        <v>0</v>
+      </c>
+      <c r="G32" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="6"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+    </row>
+    <row r="34" spans="1:7" ht="15">
       <c r="A34" s="2" t="s">
         <v>48</v>
       </c>
@@ -1411,147 +1483,397 @@
       <c r="D34" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E34" s="2">
-        <v>0</v>
-      </c>
-      <c r="F34" s="2">
-        <v>0</v>
-      </c>
-      <c r="G34" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E34" s="6">
+        <v>0</v>
+      </c>
+      <c r="F34" s="6">
+        <v>0</v>
+      </c>
+      <c r="G34" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="6"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-    </row>
-    <row r="36" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:7" ht="120" customHeight="1">
       <c r="A36" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0</v>
+      </c>
+      <c r="F36" s="6">
+        <v>0</v>
+      </c>
+      <c r="G36" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="120" customHeight="1">
+      <c r="A37" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0</v>
-      </c>
-      <c r="F36" s="8">
-        <v>0</v>
-      </c>
-      <c r="G36" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
+      <c r="B37" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0</v>
-      </c>
-      <c r="F37" s="8">
-        <v>0</v>
-      </c>
-      <c r="G37" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E37" s="6">
+        <v>0</v>
+      </c>
+      <c r="F37" s="6">
+        <v>0</v>
+      </c>
+      <c r="G37" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="120" customHeight="1">
       <c r="A38" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0</v>
-      </c>
-      <c r="F38" s="8">
-        <v>0</v>
-      </c>
-      <c r="G38" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0</v>
+      </c>
+      <c r="F38" s="6">
+        <v>0</v>
+      </c>
+      <c r="G38" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="120" customHeight="1">
       <c r="A39" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0</v>
-      </c>
-      <c r="F39" s="8">
-        <v>0</v>
-      </c>
-      <c r="G39" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
+      <c r="E39" s="6">
+        <v>0</v>
+      </c>
+      <c r="F39" s="6">
+        <v>0</v>
+      </c>
+      <c r="G39" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="99.75" customHeight="1">
+      <c r="A40" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0</v>
+      </c>
+      <c r="F40" s="6">
+        <v>0</v>
+      </c>
+      <c r="G40" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="99.75" customHeight="1">
+      <c r="A41" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0</v>
+      </c>
+      <c r="F41" s="6">
+        <v>0</v>
+      </c>
+      <c r="G41" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="99.75" customHeight="1">
+      <c r="A42" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E42" s="6">
+        <v>0</v>
+      </c>
+      <c r="F42" s="6">
+        <v>0</v>
+      </c>
+      <c r="G42" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="99.75" customHeight="1">
+      <c r="A43" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E43" s="6">
+        <v>0</v>
+      </c>
+      <c r="F43" s="6">
+        <v>0</v>
+      </c>
+      <c r="G43" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="99.75" customHeight="1">
+      <c r="A44" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7">
+        <v>0</v>
+      </c>
+      <c r="G44" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="99.75" customHeight="1">
+      <c r="A45" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0</v>
+      </c>
+      <c r="F45" s="7">
+        <v>0</v>
+      </c>
+      <c r="G45" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="99.75" customHeight="1">
+      <c r="A46" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0</v>
+      </c>
+      <c r="F46" s="7">
+        <v>0</v>
+      </c>
+      <c r="G46" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="99.75" customHeight="1">
+      <c r="A47" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E47" s="7">
+        <v>0</v>
+      </c>
+      <c r="F47" s="7">
+        <v>0</v>
+      </c>
+      <c r="G47" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="99.75" customHeight="1">
+      <c r="A48" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0</v>
+      </c>
+      <c r="F48" s="7">
+        <v>0</v>
+      </c>
+      <c r="G48" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="99.75" customHeight="1">
+      <c r="A49" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0</v>
+      </c>
+      <c r="F49" s="7">
+        <v>0</v>
+      </c>
+      <c r="G49" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="99.75" customHeight="1">
+      <c r="A50" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0</v>
+      </c>
+      <c r="F50" s="7">
+        <v>0</v>
+      </c>
+      <c r="G50" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="99.75" customHeight="1">
+      <c r="A51" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0</v>
+      </c>
+      <c r="F51" s="7">
+        <v>0</v>
+      </c>
+      <c r="G51" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15">
+      <c r="A52" s="2"/>
+    </row>
+    <row r="53" spans="1:7" ht="15">
+      <c r="A53" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
